--- a/arctrl_applications.xlsx
+++ b/arctrl_applications.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HLWei\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HLWei\source\repos\other\ARCtrl_Paper_Snippets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F6F70A2-D6D3-44A8-B6B1-F0193A9FC824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCEC2902-6AAE-40AD-962B-1DABC8689073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25510" yWindow="0" windowWidth="25780" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="51420" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -781,9 +781,6 @@
     <t>https://git.nfdi4plants.org/csbiology/morphomapper/</t>
   </si>
   <si>
-    <t>https://archive.nfdi4plants.org/records/9p24k-txz48</t>
-  </si>
-  <si>
     <t>BrAPI2ARC</t>
   </si>
   <si>
@@ -821,6 +818,9 @@
   </si>
   <si>
     <t xml:space="preserve">Python </t>
+  </si>
+  <si>
+    <t>https://doi.org/10.60534/jdyk4-w2e24</t>
   </si>
 </sst>
 </file>
@@ -912,7 +912,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -926,6 +926,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1255,7 +1256,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -1365,7 +1366,7 @@
         <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D9" t="s">
         <v>34</v>
@@ -1512,7 +1513,7 @@
         <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D18" t="s">
         <v>64</v>
@@ -1686,53 +1687,53 @@
       <c r="D29" t="s">
         <v>103</v>
       </c>
-      <c r="E29" t="s">
-        <v>104</v>
+      <c r="E29" s="5" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>106</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>45</v>
       </c>
       <c r="D30" t="s">
+        <v>106</v>
+      </c>
+      <c r="E30" t="s">
         <v>107</v>
-      </c>
-      <c r="E30" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>110</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D31" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="D32" t="s">
         <v>112</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D32" t="s">
-        <v>113</v>
       </c>
     </row>
   </sheetData>
